--- a/diseases/d102/2000-2004.xlsx
+++ b/diseases/d102/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>115</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>2.221706399953711</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>87</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>1.680769189530199</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>69</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>1.333023839972227</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>58</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>1.120512793020133</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>44</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.8500441878083765</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>40</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.7727674434621603</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>56</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>1.081874420847025</v>
       </c>
@@ -3685,9 +3664,6 @@
       <c r="O17" t="n">
         <v>58</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>1.120512793020133</v>
       </c>
@@ -4081,9 +4057,6 @@
       <c r="O19" t="n">
         <v>41</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.7920866295487144</v>
       </c>
@@ -4625,9 +4598,6 @@
       <c r="O22" t="n">
         <v>79</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>1.526215700837767</v>
       </c>
@@ -5169,9 +5139,6 @@
       <c r="O25" t="n">
         <v>61</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>1.178470351279795</v>
       </c>
@@ -5713,9 +5680,6 @@
       <c r="O28" t="n">
         <v>65</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>1.255747095626011</v>
       </c>
@@ -6257,9 +6221,6 @@
       <c r="O31" t="n">
         <v>43</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.8288404079359735</v>
       </c>
@@ -6801,9 +6762,6 @@
       <c r="O34" t="n">
         <v>10</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.1927535832409241</v>
       </c>
@@ -7345,9 +7303,6 @@
       <c r="O37" t="n">
         <v>8</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.1542028665927392</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>5</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -8433,9 +8385,6 @@
       <c r="O43" t="n">
         <v>14</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.2698550165372937</v>
       </c>
@@ -8977,9 +8926,6 @@
       <c r="O46" t="n">
         <v>29</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.5589853913986798</v>
       </c>
@@ -9521,9 +9467,6 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>1.04086934950099</v>
       </c>
@@ -10065,9 +10008,6 @@
       <c r="O52" t="n">
         <v>70</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>1.349275082686468</v>
       </c>
@@ -10609,9 +10549,6 @@
       <c r="O55" t="n">
         <v>89</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>1.715506890844224</v>
       </c>
@@ -11153,9 +11090,6 @@
       <c r="O58" t="n">
         <v>125</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>2.409419790511551</v>
       </c>
@@ -11697,9 +11631,6 @@
       <c r="O61" t="n">
         <v>246</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>4.741738147726732</v>
       </c>
@@ -12241,9 +12172,6 @@
       <c r="O64" t="n">
         <v>361</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>6.958404354997358</v>
       </c>
@@ -12785,9 +12713,6 @@
       <c r="O67" t="n">
         <v>294</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>5.653252562327109</v>
       </c>
@@ -13329,9 +13254,6 @@
       <c r="O70" t="n">
         <v>179</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>3.441946287947458</v>
       </c>
@@ -13873,9 +13795,6 @@
       <c r="O73" t="n">
         <v>174</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>3.345802536887473</v>
       </c>
@@ -14417,9 +14336,6 @@
       <c r="O76" t="n">
         <v>122</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>2.34590752586363</v>
       </c>
@@ -14961,9 +14877,6 @@
       <c r="O79" t="n">
         <v>112</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>2.153620023743661</v>
       </c>
@@ -15505,9 +15418,6 @@
       <c r="O82" t="n">
         <v>97</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>1.865188770563706</v>
       </c>
@@ -16049,9 +15959,6 @@
       <c r="O85" t="n">
         <v>172</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>3.307345036463479</v>
       </c>
@@ -16593,9 +16500,6 @@
       <c r="O88" t="n">
         <v>201</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>3.864978792611391</v>
       </c>
@@ -17137,9 +17041,6 @@
       <c r="O91" t="n">
         <v>186</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>3.576547539431437</v>
       </c>
@@ -17681,9 +17582,6 @@
       <c r="O94" t="n">
         <v>257</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>4.941788804483221</v>
       </c>
@@ -18225,9 +18123,6 @@
       <c r="O97" t="n">
         <v>465</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>8.941368848578591</v>
       </c>
@@ -18769,9 +18664,6 @@
       <c r="O100" t="n">
         <v>339</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>6.518546321866973</v>
       </c>
@@ -19313,9 +19205,6 @@
       <c r="O103" t="n">
         <v>169</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>3.241923246987553</v>
       </c>
@@ -19857,9 +19746,6 @@
       <c r="O106" t="n">
         <v>94</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>1.803199912525621</v>
       </c>
@@ -20401,9 +20287,6 @@
       <c r="O109" t="n">
         <v>106</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>2.03339564603953</v>
       </c>
@@ -20945,9 +20828,6 @@
       <c r="O112" t="n">
         <v>97</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>1.860748845904099</v>
       </c>
@@ -21489,9 +21369,6 @@
       <c r="O115" t="n">
         <v>117</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>2.244408401760614</v>
       </c>
@@ -22033,9 +21910,6 @@
       <c r="O118" t="n">
         <v>146</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>2.800714757752561</v>
       </c>
@@ -22577,9 +22451,6 @@
       <c r="O121" t="n">
         <v>194</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>3.721497691808197</v>
       </c>
@@ -23121,9 +22992,6 @@
       <c r="O124" t="n">
         <v>167</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>3.203557291401902</v>
       </c>
@@ -23665,9 +23533,6 @@
       <c r="O127" t="n">
         <v>116</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>2.225225423967788</v>
       </c>
@@ -24209,9 +24074,6 @@
       <c r="O130" t="n">
         <v>144</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>2.762348802166909</v>
       </c>
@@ -24753,9 +24615,6 @@
       <c r="O133" t="n">
         <v>138</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>2.647250935409955</v>
       </c>
@@ -25297,9 +25156,6 @@
       <c r="O136" t="n">
         <v>77</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>1.477089290047583</v>
       </c>
@@ -25841,9 +25697,6 @@
       <c r="O139" t="n">
         <v>73</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>1.396287939821137</v>
       </c>
@@ -26385,9 +26238,6 @@
       <c r="O142" t="n">
         <v>62</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>1.18588838724535</v>
       </c>
@@ -26929,9 +26779,6 @@
       <c r="O145" t="n">
         <v>46</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.87985267440784</v>
       </c>
@@ -27473,9 +27320,6 @@
       <c r="O148" t="n">
         <v>37</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.7077075859367409</v>
       </c>
@@ -28017,9 +27861,6 @@
       <c r="O151" t="n">
         <v>56</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>1.071124994931284</v>
       </c>
@@ -28561,9 +28402,6 @@
       <c r="O154" t="n">
         <v>58</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>1.109379459035972</v>
       </c>
@@ -29105,9 +28943,6 @@
       <c r="O157" t="n">
         <v>85</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>1.62581472444927</v>
       </c>
@@ -29649,9 +29484,6 @@
       <c r="O160" t="n">
         <v>120</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>2.295267846281322</v>
       </c>
@@ -30193,9 +30025,6 @@
       <c r="O163" t="n">
         <v>118</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>2.257013382176633</v>
       </c>
@@ -30737,9 +30566,6 @@
       <c r="O166" t="n">
         <v>149</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>2.849957575799308</v>
       </c>
@@ -31281,9 +31107,6 @@
       <c r="O169" t="n">
         <v>305</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>5.833805775965026</v>
       </c>
@@ -31824,9 +31647,6 @@
       </c>
       <c r="O172" t="n">
         <v>321</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>0</v>
       </c>
       <c r="R172" t="n">
         <v>6.139841488802535</v>
